--- a/Orçado/Orça-Despesas Tributarias/Despesas Tributarias.xlsx
+++ b/Orçado/Orça-Despesas Tributarias/Despesas Tributarias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Orçado\Orça-Despesas Administrativas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Orçado\Orça-Despesas Tributarias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22E79A3E-7FEC-4B94-AEAF-4EB0461BFAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B23BD6-D597-4594-AC65-F540F7C88208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8DCB4947-45C2-4345-AA02-FA9A4EA43EA0}"/>
   </bookViews>
